--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反映の記録" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'動作'!$A$1:$H$8</definedName>
   </definedNames>
@@ -62,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -82,11 +82,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -116,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -133,9 +128,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -669,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -798,47 +790,43 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>MENU_DROP_STYLE</t>
+          <t>MENU_DROP_STYLE_COMPASS</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニューの項目 (落とし先の見せ方を切り替える)</t>
+          <t>「TP_GUIdocker」メニューの切り替え項目 (十字ボタン式の時。選ぶと区画の領域式に切り替わる)</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>落とし先の表示を切り替え</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>「落とし先」がよく分からない　実態を実装後に確認して適切な単語を充てたい</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+          <t>ドラッグ時の表示:十字ボタン式</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>RETURN_AUTO</t>
+          <t>MENU_DROP_STYLE_REGION</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>「戻り先レイアウトを選ぶ」の一覧の先頭</t>
+          <t>同上 (区画の領域式の時。選ぶと十字ボタン式に切り替わる)</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>自動 (有効化する直前の配置)</t>
+          <t>ドラッグ時の表示:区画の領域式</t>
         </is>
       </c>
       <c r="D7" s="8" t="n"/>
@@ -851,17 +839,17 @@
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>COVER</t>
+          <t>RETURN_AUTO</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>起動時、準備が整うまで本体の画面を覆う表示</t>
+          <t>「戻り先レイアウトを選ぶ」の一覧の先頭</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdockerを有効化しています…</t>
+          <t>自動 (有効化する直前の配置)</t>
         </is>
       </c>
       <c r="D8" s="8" t="n"/>
@@ -874,15 +862,19 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>EMPTY_AREA</t>
+          <t>COVER</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>パネルが1枚も無い区画の中央</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr"/>
+          <t>起動時、準備が整うまで本体の画面を覆う表示</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>TP_GUIdockerを有効化しています…</t>
+        </is>
+      </c>
       <c r="D9" s="8" t="n"/>
       <c r="E9" s="9" t="inlineStr">
         <is>
@@ -890,144 +882,140 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="120" customHeight="1">
+    <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
+          <t>EMPTY_AREA</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>パネルが1枚も無い区画の中央</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
           <t>CONFIRM_FIRST</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>初めて有効化する時の確認 (%lu は本体バージョン)</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdockerを有効化します。
 本体の画面に手を加える機能のため、不具合が起きた場合は「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で元に戻せます。
 有効化しますか？ (本体バージョン %lu)</t>
         </is>
       </c>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>CONFIRM_HOST_UPDATED</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>本体の更新を検知した時の確認 (%lu は旧・新バージョン)</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>AviUtl2本体が更新されています (%lu → %lu)。
 TP_GUIdockerはこのバージョンで未確認です。不具合が起きる可能性があります。
 有効化しますか？</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>FAIL_TITLE</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>有効化に失敗した時の知らせ (先頭)</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">TP_GUIdockerを有効化できませんでした。
 理由: </t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>FAIL_RESTORED</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>同上 (標準の画面に戻せた場合の末尾)</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">
 無効化しました。</t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>FAIL_NOT_RESTORED</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>同上 (戻せなかった場合の末尾)</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">
 「表示」→「レイアウト」から普段の配置を選んで戻してください。</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>REASON_SAVE_CURRENT</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>失敗の理由</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>現在の配置を本体に保存させることができませんでした。</t>
-        </is>
-      </c>
       <c r="D15" s="8" t="n"/>
       <c r="E15" s="9" t="inlineStr">
         <is>
@@ -1038,7 +1026,7 @@
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>REASON_REGISTER</t>
+          <t>REASON_SAVE_CURRENT</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -1048,7 +1036,7 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdocker用のレイアウトを本体に登録できませんでした。</t>
+          <t>現在の配置を本体に保存させることができませんでした。</t>
         </is>
       </c>
       <c r="D16" s="8" t="n"/>
@@ -1061,7 +1049,7 @@
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>REASON_READ_SAVED</t>
+          <t>REASON_REGISTER</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -1071,7 +1059,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>保存した配置を読み込めませんでした。</t>
+          <t>TP_GUIdocker用のレイアウトを本体に登録できませんでした。</t>
         </is>
       </c>
       <c r="D17" s="8" t="n"/>
@@ -1084,7 +1072,7 @@
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>REASON_WRITE</t>
+          <t>REASON_READ_SAVED</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -1094,7 +1082,7 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdocker用のレイアウトを書き出せませんでした。</t>
+          <t>保存した配置を読み込めませんでした。</t>
         </is>
       </c>
       <c r="D18" s="8" t="n"/>
@@ -1107,7 +1095,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>REASON_LOAD_FAILED</t>
+          <t>REASON_WRITE</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1117,7 +1105,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>本体がレイアウトの読み込みに失敗しました。</t>
+          <t>TP_GUIdocker用のレイアウトを書き出せませんでした。</t>
         </is>
       </c>
       <c r="D19" s="8" t="n"/>
@@ -1130,7 +1118,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>REASON_NOT_IN_MENU</t>
+          <t>REASON_LOAD_FAILED</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1140,7 +1128,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdocker用のレイアウトがメニューに見つかりません。</t>
+          <t>本体がレイアウトの読み込みに失敗しました。</t>
         </is>
       </c>
       <c r="D20" s="8" t="n"/>
@@ -1153,17 +1141,17 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>REASON_MISSING</t>
+          <t>REASON_NOT_IN_MENU</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>失敗の理由 (%s は切り離されなかったパネル)</t>
+          <t>失敗の理由</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>一部のパネルが本体に切り離されませんでした (%s)。</t>
+          <t>TP_GUIdocker用のレイアウトがメニューに見つかりません。</t>
         </is>
       </c>
       <c r="D21" s="8" t="n"/>
@@ -1176,17 +1164,17 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>REASON_CAPTURE</t>
+          <t>REASON_MISSING</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>失敗の理由 (%s はパネル)</t>
+          <t>失敗の理由 (%s は切り離されなかったパネル)</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>パネル(%s)を取り込めませんでした。</t>
+          <t>一部のパネルが本体に切り離されませんでした (%s)。</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
@@ -1196,57 +1184,57 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
+          <t>REASON_CAPTURE</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>失敗の理由 (%s はパネル)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>パネル(%s)を取り込めませんでした。</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
           <t>EXPLORER_NOTICE</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>有効中にメディアエクスプローラーを開こうとした時の案内</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>メディアエクスプローラーは、TP_GUIdockerの有効中は使えません。
 「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で標準の画面に戻すと使えます。</t>
         </is>
       </c>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>TAB_FLOAT</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>タブの右クリックメニュー</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>分離する</t>
-        </is>
-      </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>TAB_CLOSE</t>
+          <t>TAB_FLOAT</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
@@ -1256,89 +1244,89 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>閉じる</t>
+          <t>分離する</t>
         </is>
       </c>
       <c r="D25" s="8" t="n"/>
-      <c r="E25" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>TAB_MOVE_TO</t>
+          <t>TAB_CLOSE</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>タブの右クリックメニュー (下に区画の一覧が出る)</t>
+          <t>タブの右クリックメニュー</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>他の区画へ移動</t>
+          <t>閉じる</t>
         </is>
       </c>
       <c r="D26" s="8" t="n"/>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>TAB_SPLIT</t>
+          <t>TAB_MOVE_TO</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>タブの右クリックメニュー (下に分割の向きが出る)</t>
+          <t>タブの右クリックメニュー (下に区画の一覧が出る)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>この区画を分割</t>
+          <t>他の区画へ移動</t>
         </is>
       </c>
       <c r="D27" s="8" t="n"/>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>SPLIT_LEFT</t>
+          <t>TAB_SPLIT</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>「この区画を分割」の下の項目</t>
+          <t>タブの右クリックメニュー (下に分割の向きが出る)</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>左に空き区画を作る</t>
+          <t>この区画を分割</t>
         </is>
       </c>
       <c r="D28" s="8" t="n"/>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>SPLIT_RIGHT</t>
+          <t>SPLIT_LEFT</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
@@ -1348,20 +1336,20 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>右に空き区画を作る</t>
+          <t>左に空き区画を作る</t>
         </is>
       </c>
       <c r="D29" s="8" t="n"/>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>SPLIT_TOP</t>
+          <t>SPLIT_RIGHT</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
@@ -1371,20 +1359,20 @@
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>上に空き区画を作る</t>
+          <t>右に空き区画を作る</t>
         </is>
       </c>
       <c r="D30" s="8" t="n"/>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>SPLIT_BOTTOM</t>
+          <t>SPLIT_TOP</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
@@ -1394,157 +1382,134 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>下に空き区画を作る</t>
+          <t>上に空き区画を作る</t>
         </is>
       </c>
       <c r="D31" s="8" t="n"/>
-      <c r="E31" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>AREA_NAME_FORMAT</t>
+          <t>SPLIT_BOTTOM</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>「他の区画へ移動」の一覧での区画の呼び名 (%s は区画の表示中パネル名)</t>
+          <t>「この区画を分割」の下の項目</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>%sの区画</t>
+          <t>下に空き区画を作る</t>
         </is>
       </c>
       <c r="D32" s="8" t="n"/>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>AREA_NAME_EMPTY</t>
+          <t>AREA_NAME_FORMAT</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>同上 (空き区画の呼び名。%d は番号)</t>
+          <t>「他の区画へ移動」の一覧での区画の呼び名 (%s は区画の表示中パネル名)</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>空き区画%d</t>
+          <t>%sの区画</t>
         </is>
       </c>
       <c r="D33" s="8" t="n"/>
-      <c r="E33" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>DROP_STYLE_COMPASS</t>
+          <t>AREA_NAME_EMPTY</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>落とし先の表示の切り替え時の知らせ</t>
+          <t>同上 (空き区画の呼び名。%d は番号)</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>落とし先の表示:十字ボタン式</t>
+          <t>空き区画%d</t>
         </is>
       </c>
       <c r="D34" s="8" t="n"/>
-      <c r="E34" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>DROP_STYLE_REGION</t>
+          <t>AREA_CLOSE</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>空き区画の右クリックメニュー</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>落とし先の表示:区画の領域式</t>
+          <t>この区画を閉じる</t>
         </is>
       </c>
       <c r="D35" s="8" t="n"/>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="18" customHeight="1">
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>AREA_CLOSE</t>
+          <t>DOCK_UNKNOWN_PANEL</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>空き区画の右クリックメニュー</t>
+          <t>照合できなかった浮いた窓を区画へ入れようとした時の知らせ</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>この区画を閉じる</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>DOCK_UNKNOWN_PANEL</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>照合できなかった浮いた窓を区画へ入れようとした時の知らせ</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>このパネルは識別できないため、区画に入れられません。
 一度閉じて「表示」メニューから開き直してください。</t>
         </is>
       </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E37"/>
+  <autoFilter ref="A1:E36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1980,7 +1945,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>落とし先の予告表示の色</t>
+          <t>配置ガイドの予告表示の色</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1994,9 +1959,9 @@
         </is>
       </c>
       <c r="E14" s="8" t="n"/>
-      <c r="F14" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -2013,7 +1978,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>落とし先の予告表示の濃さ</t>
+          <t>配置ガイドの予告表示の濃さ</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -2027,9 +1992,9 @@
         </is>
       </c>
       <c r="E15" s="8" t="n"/>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr"/>
@@ -2056,9 +2021,9 @@
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -2089,9 +2054,9 @@
         </is>
       </c>
       <c r="E17" s="8" t="n"/>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -2122,9 +2087,9 @@
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr"/>
@@ -2223,9 +2188,9 @@
         </is>
       </c>
       <c r="F2" s="8" t="n"/>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H2" s="7" t="inlineStr">
@@ -2261,9 +2226,9 @@
         </is>
       </c>
       <c r="F3" s="8" t="n"/>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr"/>
@@ -2276,7 +2241,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>落とし先の見せ方</t>
+          <t>配置ガイドの方式</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -2291,14 +2256,14 @@
       </c>
       <c r="E4" s="7" t="inlineStr"/>
       <c r="F4" s="8" t="n"/>
-      <c r="G4" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>メニューで切り替えて使い比べられる</t>
+          <t>メニュー「ドラッグ時の表示」で切り替えられる。両方を残す (利用者の指定)</t>
         </is>
       </c>
     </row>
@@ -2325,9 +2290,9 @@
       </c>
       <c r="E5" s="7" t="inlineStr"/>
       <c r="F5" s="8" t="n"/>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr"/>
@@ -2355,9 +2320,9 @@
       </c>
       <c r="E6" s="7" t="inlineStr"/>
       <c r="F6" s="8" t="n"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -2385,9 +2350,9 @@
       <c r="D7" s="7" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr"/>
       <c r="F7" s="8" t="n"/>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>段階2で実装</t>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr"/>
@@ -2446,32 +2411,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>シート</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>いただいた指示</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>対応</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
@@ -2500,12 +2465,12 @@
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>実装後に実物を確認いただいたうえで、呼び名を相談して決める</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>相談中</t>
+          <t>「配置ガイド」は開発上の呼び名とし画面には出さない (利用者の指定)。メニューは今の方式を示す切り替え項目「ドラッグ時の表示:十字ボタン式／区画の領域式」に変更し、切り替え時の知らせは廃止</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
         </is>
       </c>
     </row>

--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -14,9 +14,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反映の記録" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'動作'!$A$1:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'動作'!$A$1:$H$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1508,8 +1508,514 @@
         </is>
       </c>
     </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>WS_DEFAULT_NAME</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>最初のワークスペースの名前</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>標準</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>WS_NEW_NAME</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>「＋」で作るワークスペースの名前の初期値 (%d は番号)</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペース%d</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>WS_ADD</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースの帯の追加ボタン</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>＋</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>WS_MENU_RENAME</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースのボタンの右クリックメニュー</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>名前を変更</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>WS_MENU_SAVE</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>今の配置で上書き保存</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="n"/>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>WS_MENU_RESET</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>保存時の配置に戻す</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>WS_MENU_DELETE</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>削除</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>WS_DELETE_CONFIRM</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースを削除する時の確認 (%s は名前)</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペース「%s」を削除しますか？</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>WS_DELETE_LAST</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>最後の1つを削除しようとした時の知らせ</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
+        <is>
+          <t>最後のワークスペースは削除できません。</t>
+        </is>
+      </c>
+      <c r="D45" s="8" t="n"/>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>WS_NAME_TITLE</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>名前を入力する画面の題名</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースの名前</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>WS_NAME_LABEL</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>名前を入力する画面の説明</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>名前:</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="n"/>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>BUTTON_OK</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>名前を入力する画面のボタン</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="n"/>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>BUTTON_CANCEL</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>名前を入力する画面のボタン</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>キャンセル</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="n"/>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>MENU_WS_SWITCH</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」→「ワークスペース」の項目 (ショートカットキー割り当て用。%d は番号)</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペース%dに切り替え</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n"/>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>MENU_WS_GROUP</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニュー内の階層名</t>
+        </is>
+      </c>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペース</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>MENU_MAXIMIZE</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニューの項目 (ショートカットキー割り当て用。カーソルの下のパネルを最大化・元に戻す)</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>パネルを最大化・元に戻す</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="n"/>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>TAB_MAXIMIZE</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>タブの右クリックメニュー (通常時)</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>最大化</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>TAB_RESTORE</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>タブの右クリックメニュー (最大化中)</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>元の大きさに戻す</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>MENU_LOCK</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニューの切り替え項目 (ロックしていない時)</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>レイアウトをロック</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="n"/>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>MENU_UNLOCK</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>同上 (ロック中)</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>レイアウトのロックを解除</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="n"/>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_BADGE</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>ロック中、ワークスペースの帯の右端に出る表示 (クリックで解除)</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>ロック中</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="n"/>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>UNLOCK_BADGE</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>ロックしていない時、ワークスペースの帯の右端に出る表示 (クリックでロック)</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>ロック</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n"/>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E36"/>
+  <autoFilter ref="A1:E58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1520,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2094,8 +2600,99 @@
       </c>
       <c r="G18" s="7" t="inlineStr"/>
     </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>WS_BAR_HEIGHT</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースの帯の高さ</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>本体設定 (GroupTabHeight, 既定24)</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>px (96dpi換算)</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="n"/>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>タブ帯と同じ高さ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>WS_BUTTON_PADDING</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースのボタンの文字の左右の余白</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>px (96dpi換算)</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>COLOR_WS_ACTIVE</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>選択中のワークスペースのボタンの色</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>本体設定 (ButtonBodySelect)</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>色</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2106,7 +2703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2387,8 +2984,140 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>WS_MAX</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>ショートカットキーで切り替えられるワークスペースの数</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>1〜9</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>個</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペース自体はいくつでも作れる</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>WS_KEEP_EDITS</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースを切り替えた時の配置</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>使用中の配置を保つ</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>使用中の配置を保つ / 保存時の配置に戻す</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>保存時の配置へは右クリック「保存時の配置に戻す」でいつでも戻せる</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>LOCK_TARGETS</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>ロック中に禁止する操作</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>タブのドラッグ・右クリックの組み替え</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>利用者の指定。境界線のドラッグと浮いた窓の取り込みは禁止しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MAXIMIZE_TARGET</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>ショートカットキーで最大化するパネル</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>カーソルの下のパネル</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>カーソルが区画の外なら、最後に操作した区画</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:H12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反映の記録" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$61</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'動作'!$A$1:$H$12</definedName>
   </definedNames>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2014,8 +2014,78 @@
         </is>
       </c>
     </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>MENU_EXPORT_SAMPLES</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニューの項目 (見本の画像を書き出す。指示用)</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>見本を書き出す</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="n"/>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>EXPORT_DONE</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>見本を書き出した時の知らせ (%s は書き出し先)</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>見本を書き出しました。
+書き出し先: %s</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>EXPORT_NEED_ACTIVE</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>無効中に見本を書き出そうとした時の知らせ</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>見本は TP_GUIdockerの有効中に書き出せます。</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E58"/>
+  <autoFilter ref="A1:E61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反映の記録" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'動作'!$A$1:$H$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="18" customHeight="1">
+    <row r="57" ht="30" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
           <t>LOCK_BADGE</t>
@@ -1976,12 +1976,12 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>ロック中、ワークスペースの帯の右端に出る表示 (クリックで解除)</t>
+          <t>ロック中、帯の右端の閉じた錠前の絵にカーソルを乗せると出る説明 (クリックで解除)</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>ロック中</t>
+          <t>ロック中 (クリックで解除)</t>
         </is>
       </c>
       <c r="D57" s="8" t="n"/>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="18" customHeight="1">
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
           <t>UNLOCK_BADGE</t>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>ロックしていない時、ワークスペースの帯の右端に出る表示 (クリックでロック)</t>
+          <t>ロックしていない時、帯の右端の開いた錠前の絵にカーソルを乗せると出る説明 (クリックでロック)</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>ロック</t>
+          <t>クリックでレイアウトをロック</t>
         </is>
       </c>
       <c r="D58" s="8" t="n"/>
@@ -2084,8 +2084,54 @@
         </is>
       </c>
     </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>WS_MENU_COLOR</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースのボタンの右クリックメニュー</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>選択中の色を変える…</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>WS_MENU_COLOR_RESET</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>選択中の色を本体設定に戻す</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="n"/>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E61"/>
+  <autoFilter ref="A1:E63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2096,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2158,12 +2204,12 @@
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (GroupTabHeight, 既定24)</t>
+          <t>メニューバーと同じ</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>px (96dpi換算)</t>
+          <t>px (96dpi換算) または「メニューバーと同じ」「本体設定」</t>
         </is>
       </c>
       <c r="E2" s="8" t="n"/>
@@ -2174,7 +2220,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>本体の style.conf に連動</t>
+          <t>上のメニューバー (「ファイル」「編集」の帯) の実際の高さに合わせる</t>
         </is>
       </c>
     </row>
@@ -2191,12 +2237,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (WindowSeparatorSize, 既定7)</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>px (96dpi換算)</t>
+          <t>% (本体設定 WindowSeparatorSize に対する割合)</t>
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -2207,7 +2253,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>本体の style.conf に連動</t>
+          <t>本体設定 (既定7) の何%にするか</t>
         </is>
       </c>
     </row>
@@ -2575,7 +2621,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr"/>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>COMPASS_BUTTON</t>
@@ -2583,12 +2629,12 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>十字ボタン式のボタン1つの大きさ</t>
+          <t>ドーナツ型のボタンの直径</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -2604,7 +2650,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>大きいほど狙いやすい</t>
+          <t>中心の円はタブとして重ねる、周りの扇形4つは上下左右に分割。大きいほど狙いやすい</t>
         </is>
       </c>
     </row>
@@ -2683,12 +2729,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (GroupTabHeight, 既定24)</t>
+          <t>メニューバーと同じ</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>px (96dpi換算)</t>
+          <t>px (96dpi換算) または「メニューバーと同じ」「本体設定」</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -2699,7 +2745,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>タブ帯と同じ高さ</t>
+          <t>上のメニューバー (「ファイル」「編集」の帯) の実際の高さに合わせる</t>
         </is>
       </c>
     </row>
@@ -2745,7 +2791,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (ButtonBodySelect)</t>
+          <t>本体設定 (ButtonBodySelect)。右クリックで自由に変更可</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2759,10 +2805,43 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースのボタンの右クリック「選択中の色を変える…」で選べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>COMPASS_HOLE</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>ドーナツ型の中心の円の大きさ</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>% (直径に対する割合)</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3198,7 +3277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3249,22 +3328,22 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>文言</t>
+          <t>見た目</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>MENU_DROP_STYLE</t>
+          <t>COLOR_WS_ACTIVE</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>「落とし先」がよく分からない　実態を実装後に確認して適切な単語を充てたい</t>
+          <t>自由に変えれたらいいなと思う</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>「配置ガイド」は開発上の呼び名とし画面には出さない (利用者の指定)。メニューは今の方式を示す切り替え項目「ドラッグ時の表示:十字ボタン式／区画の領域式」に変更し、切り替え時の知らせは廃止</t>
+          <t>ワークスペースのボタンの右クリックに「選択中の色を変える…」「選択中の色を本体設定に戻す」を追加し、Windows の色選択画面で自由に選べるようにした</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -3281,22 +3360,22 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>文言</t>
+          <t>見た目</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>FAIL_RESTORED</t>
+          <t>COMPASS_BUTTON</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>無効化しました。</t>
+          <t>現在の枠は箱の展開図のような見た目だが、中心に円のある、扇が４方向にあるドーナツ型の見た目に出来ないだろうか</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>「無効化しました。」に変更。失敗の理由の後ろに付く文のため、理由との間の空行は残した</t>
+          <t>中心に円、周りに扇形4つのドーナツ型に作り替え。扇には向きを示す矢印を付けた。項目を「直径」に変更 (150)</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -3313,22 +3392,22 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>文言</t>
+          <t>見た目</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>EMPTY_AREA</t>
+          <t>SEPARATOR</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>無地にしたい</t>
+          <t>太い　試しに今の半分にしてほしい</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>文字を表示しない (無地) ように変更</t>
+          <t>本体設定の50% (半分) に変更。割合で持たせ、指示書で調整できるようにした</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -3345,22 +3424,22 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>文言</t>
+          <t>見た目</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>MENU_RESET</t>
+          <t>WS_BAR_HEIGHT</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>配置を初期状態に戻す</t>
+          <t>高さが太すぎる　上のファイルや編集と書かれたバーの高さと同じくらいで良い</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>現在の文言と同じため変更なし</t>
+          <t>上のメニューバーの実際の高さに合わせるよう変更</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -3377,22 +3456,22 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>文言</t>
+          <t>見た目</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>DROP_STYLE_REGION</t>
+          <t>TAB_HEIGHT</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>落とし先の表示:区画の領域式</t>
+          <t>高さが太すぎる　上のファイルや編集と書かれたバーの高さと同じくらいで良い</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>指示どおりの文言に変更</t>
+          <t>上のメニューバーの実際の高さに合わせるよう変更</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -3414,17 +3493,17 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>DROP_STYLE_COMPASS</t>
+          <t>UNLOCK_BADGE</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>落とし先の表示:十字ボタン式</t>
+          <t>フリーのアイコンセットから錠前のアイコンを持ってこれないか(ロック時は錠前が閉)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>指示どおりの文言に変更</t>
+          <t>帯の右端の文字を、プラグイン自身が描く錠前の絵に変更 (ロック中は閉じた錠前、解除中は開いた錠前)。外部の絵柄は使用条件の管理が要るため使わず、同じ形を描いた。文字はカーソルを乗せた時の説明として残した</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -3446,17 +3525,17 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>AREA_NAME_EMPTY</t>
+          <t>MENU_DROP_STYLE</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>空き区画%d</t>
+          <t>「落とし先」がよく分からない　実態を実装後に確認して適切な単語を充てたい</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>指示どおりの文言に変更</t>
+          <t>「配置ガイド」は開発上の呼び名とし画面には出さない (利用者の指定)。メニューは今の方式を示す切り替え項目「ドラッグ時の表示:十字ボタン式／区画の領域式」に変更し、切り替え時の知らせは廃止</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -3478,17 +3557,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>AREA_NAME_FORMAT</t>
+          <t>FAIL_RESTORED</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>%sの区画</t>
+          <t>無効化しました。</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>指示どおりの文言に変更</t>
+          <t>「無効化しました。」に変更。失敗の理由の後ろに付く文のため、理由との間の空行は残した</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -3510,17 +3589,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>TAB_FLOAT</t>
+          <t>EMPTY_AREA</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>分離する</t>
+          <t>無地にしたい</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>指示どおりの文言に変更</t>
+          <t>文字を表示しない (無地) ように変更</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -3542,378 +3621,570 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
+          <t>MENU_RESET</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>配置を初期状態に戻す</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>現在の文言と同じため変更なし</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>DROP_STYLE_REGION</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>落とし先の表示:区画の領域式</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>DROP_STYLE_COMPASS</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>落とし先の表示:十字ボタン式</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>AREA_NAME_EMPTY</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>空き区画%d</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>AREA_NAME_FORMAT</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>%sの区画</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>TAB_FLOAT</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>分離する</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
           <t>EXPLORER_NOTICE</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>メディアエクスプローラーは、TP_GUIdockerの有効中は使えません。
 「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で標準の画面に戻すと使えます。</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>REASON_CAPTURE</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>パネル(%s)を取り込めませんでした。</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>REASON_NOT_IN_MENU</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdocker用のレイアウトがメニューに見つかりません。</t>
         </is>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>REASON_WRITE</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdocker用のレイアウトを書き出せませんでした。</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>REASON_REGISTER</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdocker用のレイアウトを本体に登録できませんでした。</t>
         </is>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>FAIL_TITLE</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">TP_GUIdockerを有効化できませんでした。
 理由: </t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>CONFIRM_HOST_UPDATED</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>AviUtl2本体が更新されています (%lu → %lu)。
 TP_GUIdockerはこのバージョンで未確認です。不具合が起きる可能性があります。
 有効化しますか？</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>CONFIRM_FIRST</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdockerを有効化します。
 本体の画面に手を加える機能のため、不具合が起きた場合は「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で元に戻せます。
 有効化しますか？ (本体バージョン %lu)</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>COVER</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdockerを有効化しています…</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>MENU_CHOOSE_RETURN</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>無効時のレイアウトを選ぶ</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>MENU_DISABLE</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdockerを無効化</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>MENU_ENABLE</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdockerを有効化</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>

--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'動作'!$A$1:$H$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="18" customHeight="1">
+    <row r="62" ht="30" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
           <t>WS_MENU_COLOR</t>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>ワークスペースのボタンの右クリックメニュー</t>
+          <t>ワークスペースのボタンの右クリックメニュー・「TP_GUIdocker」メニュー</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>選択中の色を変える…</t>
+          <t>テーマの色を変える…</t>
         </is>
       </c>
       <c r="D62" s="8" t="n"/>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>選択中の色を本体設定に戻す</t>
+          <t>テーマの色を本体設定に戻す</t>
         </is>
       </c>
       <c r="D63" s="8" t="n"/>
@@ -2142,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2191,25 +2191,25 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>TAB_HEIGHT</t>
+          <t>THEME_COLOR</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>タブ帯の高さ</t>
+          <t>テーマの色 (プラグイン全体の強調色)</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>メニューバーと同じ</t>
+          <t>本体設定 (ButtonBodySelect)。メニューで自由に変更可</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>px (96dpi換算) または「メニューバーと同じ」「本体設定」</t>
+          <t>色</t>
         </is>
       </c>
       <c r="E2" s="8" t="n"/>
@@ -2220,29 +2220,29 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>上のメニューバー (「ファイル」「編集」の帯) の実際の高さに合わせる</t>
+          <t>選択中のワークスペースのボタン・ロック中の錠前の背景・選択中のタブの下線・ドラッグ中の予告と選ばれている扇に使う。「テーマの色を変える…」で選ぶ</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>SEPARATOR</t>
+          <t>TAB_HEIGHT</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>区画の間 (境界線) の太さ</t>
+          <t>タブ帯の高さ</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>メニューバーと同じ</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>% (本体設定 WindowSeparatorSize に対する割合)</t>
+          <t>px (96dpi換算) または「メニューバーと同じ」「本体設定」</t>
         </is>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -2253,29 +2253,29 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (既定7) の何%にするか</t>
+          <t>上のメニューバー (「ファイル」「編集」の帯) の実際の高さに合わせる</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>TAB_PADDING</t>
+          <t>SEPARATOR</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>タブの文字の左右の余白</t>
+          <t>区画の間 (境界線) の太さ</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>px (96dpi換算)</t>
+          <t>% (本体設定 WindowSeparatorSize に対する割合)</t>
         </is>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -2284,22 +2284,26 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>本体設定 (既定7) の何%にするか</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>MIN_PANE</t>
+          <t>TAB_PADDING</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>区画の最小の大きさ</t>
+          <t>タブの文字の左右の余白</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
@@ -2313,26 +2317,22 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>境界線ドラッグで、これより小さくできない</t>
-        </is>
-      </c>
+      <c r="G5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>FLOAT_W</t>
+          <t>MIN_PANE</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>浮いた窓の既定の幅</t>
+          <t>区画の最小の大きさ</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -2348,24 +2348,24 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>初めて浮かせる時の大きさ</t>
+          <t>境界線ドラッグで、これより小さくできない</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>FLOAT_H</t>
+          <t>FLOAT_W</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>浮いた窓の既定の高さ</t>
+          <t>浮いた窓の既定の幅</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>640</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -2379,58 +2379,58 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>初めて浮かせる時の大きさ</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>FONT</t>
+          <t>FLOAT_H</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>タブの文字</t>
+          <t>浮いた窓の既定の高さ</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (Control, 既定 Yu Gothic UI 13)</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>px (96dpi換算)</t>
+        </is>
+      </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="9" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>本体の style.conf に連動</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
+      <c r="G8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>COLOR_TABBAR</t>
+          <t>FONT</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>タブ帯の背景色</t>
+          <t>タブ・ワークスペースの帯の文字</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (Grouping)</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>色</t>
-        </is>
-      </c>
+          <t>メニューバーと同じ</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -2439,24 +2439,24 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>本体の style.conf に連動</t>
+          <t>Windows がメニューに使う文字の種類と大きさ (帯の高さをメニューバーにそろえたため、最も自然に収まる)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>COLOR_TAB_ACTIVE</t>
+          <t>COLOR_TABBAR</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>選択中のタブの背景色</t>
+          <t>タブ帯の背景色</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (GroupingSelect)</t>
+          <t>本体設定 (Grouping)</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -2470,22 +2470,26 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>本体の style.conf に連動</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>COLOR_TAB_TEXT</t>
+          <t>COLOR_TAB_ACTIVE</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>選択中のタブの文字色</t>
+          <t>選択中のタブの背景色</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (Text)</t>
+          <t>本体設定 (GroupingSelect)</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2504,17 +2508,17 @@
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>COLOR_TAB_TEXT_OFF</t>
+          <t>COLOR_TAB_TEXT</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>選択されていないタブの文字色</t>
+          <t>選択中のタブの文字色</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (TextDisable)</t>
+          <t>本体設定 (Text)</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -2533,17 +2537,17 @@
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>COLOR_SEPARATOR</t>
+          <t>COLOR_TAB_TEXT_OFF</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>区画の間の色</t>
+          <t>選択されていないタブの文字色</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (WindowSeparator)</t>
+          <t>本体設定 (TextDisable)</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2562,17 +2566,17 @@
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>DROP_HIGHLIGHT</t>
+          <t>COLOR_SEPARATOR</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>配置ガイドの予告表示の色</t>
+          <t>区画の間の色</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>#5A8CFF</t>
+          <t>本体設定 (WindowSeparator)</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -2586,31 +2590,27 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>置かれる範囲を塗る色</t>
-        </is>
-      </c>
+      <c r="G14" s="7" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>DROP_ALPHA</t>
+          <t>DROP_HIGHLIGHT</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>配置ガイドの予告表示の濃さ</t>
+          <t>配置ガイドの予告表示の色</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>#5A8CFF</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>% (0=透明)</t>
+          <t>色</t>
         </is>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -2619,27 +2619,31 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>テーマの色を選んだ場合は、テーマの色を使う</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>COMPASS_BUTTON</t>
+          <t>DROP_ALPHA</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>ドーナツ型のボタンの直径</t>
+          <t>配置ガイドの予告表示の濃さ</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>px (96dpi換算)</t>
+          <t>% (0=透明)</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -2648,31 +2652,27 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>中心の円はタブとして重ねる、周りの扇形4つは上下左右に分割。大きいほど狙いやすい</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
+      <c r="G16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>REGION_EDGE</t>
+          <t>COMPASS_BUTTON</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>区画の領域式で、上下左右と判定する幅</t>
+          <t>ドーナツ型のボタンの直径</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>% (区画の幅・高さに対する割合)</t>
+          <t>px (96dpi換算)</t>
         </is>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -2683,29 +2683,29 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>中央の残りがタブとして重ねる領域</t>
+          <t>中心の円はタブとして重ねる、周りの扇形4つは上下左右に分割。大きいほど狙いやすい</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>DRAG_GHOST_ALPHA</t>
+          <t>REGION_EDGE</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>ドラッグ中のタブの影の濃さ</t>
+          <t>区画の領域式で、上下左右と判定する幅</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>% (0=透明)</t>
+          <t>% (区画の幅・高さに対する割合)</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -2714,27 +2714,31 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>中央の残りがタブとして重ねる領域</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>WS_BAR_HEIGHT</t>
+          <t>DRAG_GHOST_ALPHA</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>ワークスペースの帯の高さ</t>
+          <t>ドラッグ中のタブの影の濃さ</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>メニューバーと同じ</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>px (96dpi換算) または「メニューバーと同じ」「本体設定」</t>
+          <t>% (0=透明)</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -2743,31 +2747,27 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>上のメニューバー (「ファイル」「編集」の帯) の実際の高さに合わせる</t>
-        </is>
-      </c>
+      <c r="G19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>WS_BUTTON_PADDING</t>
+          <t>WS_BAR_HEIGHT</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>ワークスペースのボタンの文字の左右の余白</t>
+          <t>ワークスペースの帯の高さ</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>メニューバーと同じ</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>px (96dpi換算)</t>
+          <t>px (96dpi換算) または「メニューバーと同じ」「本体設定」</t>
         </is>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -2776,27 +2776,31 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>上のメニューバー (「ファイル」「編集」の帯) の実際の高さに合わせる</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>COLOR_WS_ACTIVE</t>
+          <t>WS_BUTTON_PADDING</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>選択中のワークスペースのボタンの色</t>
+          <t>ワークスペースのボタンの文字の左右の余白</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>本体設定 (ButtonBodySelect)。右クリックで自由に変更可</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>色</t>
+          <t>px (96dpi換算)</t>
         </is>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -2805,31 +2809,27 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>ワークスペースのボタンの右クリック「選択中の色を変える…」で選べる</t>
-        </is>
-      </c>
+      <c r="G21" s="7" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>COMPASS_HOLE</t>
+          <t>COLOR_WS_ACTIVE</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>ドーナツ型の中心の円の大きさ</t>
+          <t>選択中のワークスペースのボタンの色</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>テーマの色</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>% (直径に対する割合)</t>
+          <t>色</t>
         </is>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -2838,10 +2838,76 @@
           <t>実装済み</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>THEME_COLOR を使う</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>COMPASS_HOLE</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>ドーナツ型の中心の円の大きさ</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>% (直径に対する割合)</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="n"/>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>TAB_ACTIVE_LINE</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>選択中のタブの下線の太さ (色はテーマの色)</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>px (96dpi換算)</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>0 で下線なし</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G22"/>
+  <autoFilter ref="A1:G24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3277,7 +3343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3338,12 +3404,12 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>自由に変えれたらいいなと思う</t>
+          <t>ここだけでなく、全体のテーマの色として好きな色1色を設定できたら良いなと思う</t>
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr">
         <is>
-          <t>ワークスペースのボタンの右クリックに「選択中の色を変える…」「選択中の色を本体設定に戻す」を追加し、Windows の色選択画面で自由に選べるようにした</t>
+          <t>好きな色1色を「テーマの色」として選べるようにした。ワークスペースのボタン・錠前の背景・選択中のタブの下線 (新設)・ドラッグ中の予告と選ばれている扇に使う。「TP_GUIdocker」メニューとワークスペースの右クリックの「テーマの色を変える…」で選ぶ。前回選んだ色はテーマの色として引き継ぐ</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
@@ -3365,17 +3431,17 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>COMPASS_BUTTON</t>
+          <t>TAB_HEIGHT</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>現在の枠は箱の展開図のような見た目だが、中心に円のある、扇が４方向にあるドーナツ型の見た目に出来ないだろうか</t>
+          <t>文字サイズが大きい　この高さに合った自然な文字サイズにしてほしい</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>中心に円、周りに扇形4つのドーナツ型に作り替え。扇には向きを示す矢印を付けた。項目を「直径」に変更 (150)</t>
+          <t>帯の文字を、メニューバーの文字 (Windows がメニューに使う文字の種類と大きさ) に合わせた (見た目 FONT)</t>
         </is>
       </c>
       <c r="F3" s="9" t="inlineStr">
@@ -3397,17 +3463,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>SEPARATOR</t>
+          <t>COLOR_WS_ACTIVE</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>太い　試しに今の半分にしてほしい</t>
+          <t>自由に変えれたらいいなと思う</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>本体設定の50% (半分) に変更。割合で持たせ、指示書で調整できるようにした</t>
+          <t>ワークスペースのボタンの右クリックに「選択中の色を変える…」「選択中の色を本体設定に戻す」を追加し、Windows の色選択画面で自由に選べるようにした</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -3429,17 +3495,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>WS_BAR_HEIGHT</t>
+          <t>COMPASS_BUTTON</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>高さが太すぎる　上のファイルや編集と書かれたバーの高さと同じくらいで良い</t>
+          <t>現在の枠は箱の展開図のような見た目だが、中心に円のある、扇が４方向にあるドーナツ型の見た目に出来ないだろうか</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>上のメニューバーの実際の高さに合わせるよう変更</t>
+          <t>中心に円、周りに扇形4つのドーナツ型に作り替え。扇には向きを示す矢印を付けた。項目を「直径」に変更 (150)</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -3461,17 +3527,17 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>TAB_HEIGHT</t>
+          <t>SEPARATOR</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>高さが太すぎる　上のファイルや編集と書かれたバーの高さと同じくらいで良い</t>
+          <t>太い　試しに今の半分にしてほしい</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>上のメニューバーの実際の高さに合わせるよう変更</t>
+          <t>本体設定の50% (半分) に変更。割合で持たせ、指示書で調整できるようにした</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -3488,22 +3554,22 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>文言</t>
+          <t>見た目</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>UNLOCK_BADGE</t>
+          <t>WS_BAR_HEIGHT</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>フリーのアイコンセットから錠前のアイコンを持ってこれないか(ロック時は錠前が閉)</t>
+          <t>高さが太すぎる　上のファイルや編集と書かれたバーの高さと同じくらいで良い</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>帯の右端の文字を、プラグイン自身が描く錠前の絵に変更 (ロック中は閉じた錠前、解除中は開いた錠前)。外部の絵柄は使用条件の管理が要るため使わず、同じ形を描いた。文字はカーソルを乗せた時の説明として残した</t>
+          <t>上のメニューバーの実際の高さに合わせるよう変更</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -3520,22 +3586,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>文言</t>
+          <t>見た目</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>MENU_DROP_STYLE</t>
+          <t>TAB_HEIGHT</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>「落とし先」がよく分からない　実態を実装後に確認して適切な単語を充てたい</t>
+          <t>高さが太すぎる　上のファイルや編集と書かれたバーの高さと同じくらいで良い</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>「配置ガイド」は開発上の呼び名とし画面には出さない (利用者の指定)。メニューは今の方式を示す切り替え項目「ドラッグ時の表示:十字ボタン式／区画の領域式」に変更し、切り替え時の知らせは廃止</t>
+          <t>上のメニューバーの実際の高さに合わせるよう変更</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -3557,17 +3623,17 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>FAIL_RESTORED</t>
+          <t>UNLOCK_BADGE</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>無効化しました。</t>
+          <t>フリーのアイコンセットから錠前のアイコンを持ってこれないか(ロック時は錠前が閉)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>「無効化しました。」に変更。失敗の理由の後ろに付く文のため、理由との間の空行は残した</t>
+          <t>帯の右端の文字を、プラグイン自身が描く錠前の絵に変更 (ロック中は閉じた錠前、解除中は開いた錠前)。外部の絵柄は使用条件の管理が要るため使わず、同じ形を描いた。文字はカーソルを乗せた時の説明として残した</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -3589,17 +3655,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>EMPTY_AREA</t>
+          <t>MENU_DROP_STYLE</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>無地にしたい</t>
+          <t>「落とし先」がよく分からない　実態を実装後に確認して適切な単語を充てたい</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>文字を表示しない (無地) ように変更</t>
+          <t>「配置ガイド」は開発上の呼び名とし画面には出さない (利用者の指定)。メニューは今の方式を示す切り替え項目「ドラッグ時の表示:十字ボタン式／区画の領域式」に変更し、切り替え時の知らせは廃止</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
@@ -3621,17 +3687,17 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>MENU_RESET</t>
+          <t>FAIL_RESTORED</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>配置を初期状態に戻す</t>
+          <t>無効化しました。</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>現在の文言と同じため変更なし</t>
+          <t>「無効化しました。」に変更。失敗の理由の後ろに付く文のため、理由との間の空行は残した</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -3653,17 +3719,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>DROP_STYLE_REGION</t>
+          <t>EMPTY_AREA</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>落とし先の表示:区画の領域式</t>
+          <t>無地にしたい</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>指示どおりの文言に変更</t>
+          <t>文字を表示しない (無地) ように変更</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
@@ -3685,17 +3751,17 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>DROP_STYLE_COMPASS</t>
+          <t>MENU_RESET</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>落とし先の表示:十字ボタン式</t>
+          <t>配置を初期状態に戻す</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>指示どおりの文言に変更</t>
+          <t>現在の文言と同じため変更なし</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
@@ -3717,12 +3783,12 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>AREA_NAME_EMPTY</t>
+          <t>DROP_STYLE_REGION</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>空き区画%d</t>
+          <t>落とし先の表示:区画の領域式</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
@@ -3749,12 +3815,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>AREA_NAME_FORMAT</t>
+          <t>DROP_STYLE_COMPASS</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>%sの区画</t>
+          <t>落とし先の表示:十字ボタン式</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -3781,12 +3847,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>TAB_FLOAT</t>
+          <t>AREA_NAME_EMPTY</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>分離する</t>
+          <t>空き区画%d</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -3813,79 +3879,79 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
+          <t>AREA_NAME_FORMAT</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>%sの区画</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>TAB_FLOAT</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>分離する</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
           <t>EXPLORER_NOTICE</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>メディアエクスプローラーは、TP_GUIdockerの有効中は使えません。
 「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で標準の画面に戻すと使えます。</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>指示どおりの文言に変更</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>反映済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>文言</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>REASON_CAPTURE</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>パネル(%s)を取り込めませんでした。</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>指示どおりの文言に変更</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>反映済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>文言</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>REASON_NOT_IN_MENU</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>TP_GUIdocker用のレイアウトがメニューに見つかりません。</t>
-        </is>
-      </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
@@ -3910,12 +3976,12 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>REASON_WRITE</t>
+          <t>REASON_CAPTURE</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdocker用のレイアウトを書き出せませんでした。</t>
+          <t>パネル(%s)を取り込めませんでした。</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
@@ -3942,12 +4008,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>REASON_REGISTER</t>
+          <t>REASON_NOT_IN_MENU</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdocker用のレイアウトを本体に登録できませんでした。</t>
+          <t>TP_GUIdocker用のレイアウトがメニューに見つかりません。</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
@@ -3974,147 +4040,147 @@
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
+          <t>REASON_WRITE</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>TP_GUIdocker用のレイアウトを書き出せませんでした。</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>REASON_REGISTER</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>TP_GUIdocker用のレイアウトを本体に登録できませんでした。</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
           <t>FAIL_TITLE</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">TP_GUIdockerを有効化できませんでした。
 理由: </t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>CONFIRM_HOST_UPDATED</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>AviUtl2本体が更新されています (%lu → %lu)。
 TP_GUIdockerはこのバージョンで未確認です。不具合が起きる可能性があります。
 有効化しますか？</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>文言</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>CONFIRM_FIRST</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdockerを有効化します。
 本体の画面に手を加える機能のため、不具合が起きた場合は「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で元に戻せます。
 有効化しますか？ (本体バージョン %lu)</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>指示どおりの文言に変更</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>反映済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>文言</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>COVER</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>TP_GUIdockerを有効化しています…</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>指示どおりの文言に変更</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>反映済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>文言</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>MENU_CHOOSE_RETURN</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>無効時のレイアウトを選ぶ</t>
-        </is>
-      </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
@@ -4139,12 +4205,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>MENU_DISABLE</t>
+          <t>COVER</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdockerを無効化</t>
+          <t>TP_GUIdockerを有効化しています…</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
@@ -4171,20 +4237,84 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
+          <t>MENU_CHOOSE_RETURN</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>無効時のレイアウトを選ぶ</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>MENU_DISABLE</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>TP_GUIdockerを無効化</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>指示どおりの文言に変更</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>文言</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
           <t>MENU_ENABLE</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdockerを有効化</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>指示どおりの文言に変更</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr">
         <is>
           <t>反映済み</t>
         </is>

--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反映の記録" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'動作'!$A$1:$H$12</definedName>
   </definedNames>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="18" customHeight="1">
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
           <t>MENU_WS_GROUP</t>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニュー内の階層名</t>
+          <t>「TP_GUIdocker」メニュー内の小分けの見出し (ワークスペース1〜9に切り替え)</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -2130,8 +2130,77 @@
         </is>
       </c>
     </row>
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>MENU_GROUP_VIEW</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニュー内の小分けの見出し (ドラッグ時の表示・テーマの色)</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>表示の設定</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n"/>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>MENU_GROUP_LAYOUT</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニュー内の小分けの見出し (配置を初期状態に戻す・無効時のレイアウトを選ぶ)</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>配置の設定</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="n"/>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>MENU_GROUP_TOOLS</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニュー内の小分けの見出し (見本を書き出す)</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>指示用</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="n"/>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E63"/>
+  <autoFilter ref="A1:E66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -2483,7 +2483,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr"/>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>FONT</t>
@@ -2491,15 +2491,19 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>タブ・ワークスペースの帯の文字</t>
+          <t>タブ・ワークスペースの帯の文字の書体</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>メニューバーと同じ</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+          <t>IBM Plex Sans JP</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>書体</t>
+        </is>
+      </c>
       <c r="E9" s="8" t="n"/>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -2508,7 +2512,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Windows がメニューに使う文字の種類と大きさ (帯の高さをメニューバーにそろえたため、最も自然に収まる)</t>
+          <t>書体名で指定 (「メニューバーと同じ」も可)。大きさはメニューバーの文字と同じ。パソコンに無い書体は、プラグインと同じ場所の「TP_GUIdocker_フォント」フォルダに置けば使える。見つからない時はメニューバーと同じ書体になる。候補の比較は docs/TP_GUIdocker_フォント比較.pdf</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4389,6 +4393,38 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>見た目</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>FONT</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>フォント比較の見本から IBM Plex Sans JP に決定</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>帯とタブの文字を IBM Plex Sans JP に変更し、書体名で指定できるようにした (書体はプラグインに同梱)</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -2512,7 +2512,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>書体名で指定 (「メニューバーと同じ」も可)。大きさはメニューバーの文字と同じ。パソコンに無い書体は、プラグインと同じ場所の「TP_GUIdocker_フォント」フォルダに置けば使える。見つからない時はメニューバーと同じ書体になる。候補の比較は docs/TP_GUIdocker_フォント比較.pdf</t>
+          <t>書体名で指定 (「メニューバーと同じ」も可)。大きさはメニューバーの文字と同じ。パソコンに無い書体は、プラグインと同じ場所の「TP_GUIdocker_fonts」フォルダに置けば使える。見つからない時はメニューバーと同じ書体になる。候補の比較は docs/TP_GUIdocker_フォント比較.pdf</t>
         </is>
       </c>
     </row>

--- a/docs/TP_GUIdocker_指示書.xlsx
+++ b/docs/TP_GUIdocker_指示書.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="反映の記録" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'文言'!$A$1:$E$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'見た目'!$A$1:$G$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'動作'!$A$1:$H$12</definedName>
   </definedNames>
@@ -661,7 +661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>起動時、準備が整うまで本体の画面を覆う表示</t>
+          <t>有効化の間 (起動時・手動)、準備が整うまで本体の画面を覆う表示</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -885,15 +885,19 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>EMPTY_AREA</t>
+          <t>COVER_DISABLE</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>パネルが1枚も無い区画の中央</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr"/>
+          <t>無効化・終了の間、本体の画面を覆う表示</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>TP_GUIdockerを無効化しています…</t>
+        </is>
+      </c>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="9" t="inlineStr">
         <is>
@@ -901,190 +905,187 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="120" customHeight="1">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
+          <t>COVER_SWITCH</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースの切り替えで配置を作り直す間、本体の画面を覆う表示</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>ワークスペースを切り替えています…</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>LAYOUT_BLOCKED</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>有効中に「表示」→「レイアウト」の項目を選んだ時の案内</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>TP_GUIdockerの有効中は、レイアウトの切り替え・作成はできません。
+「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で標準の画面に戻してから選んでください。</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>EMPTY_AREA</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>パネルが1枚も無い区画の中央</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
           <t>CONFIRM_FIRST</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>初めて有効化する時の確認 (%lu は本体バージョン)</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>TP_GUIdockerを有効化します。
 本体の画面に手を加える機能のため、不具合が起きた場合は「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で元に戻せます。
 有効化しますか？ (本体バージョン %lu)</t>
         </is>
       </c>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>CONFIRM_HOST_UPDATED</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>本体の更新を検知した時の確認 (%lu は旧・新バージョン)</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>AviUtl2本体が更新されています (%lu → %lu)。
 TP_GUIdockerはこのバージョンで未確認です。不具合が起きる可能性があります。
 有効化しますか？</t>
         </is>
       </c>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>FAIL_TITLE</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>有効化に失敗した時の知らせ (先頭)</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">TP_GUIdockerを有効化できませんでした。
 理由: </t>
         </is>
       </c>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>FAIL_RESTORED</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>同上 (標準の画面に戻せた場合の末尾)</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">
 無効化しました。</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>FAIL_NOT_RESTORED</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>同上 (戻せなかった場合の末尾)</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">
 「表示」→「レイアウト」から普段の配置を選んで戻してください。</t>
         </is>
       </c>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>REASON_SAVE_CURRENT</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>失敗の理由</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>現在の配置を本体に保存させることができませんでした。</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>REASON_REGISTER</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>失敗の理由</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>TP_GUIdocker用のレイアウトを本体に登録できませんでした。</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>REASON_READ_SAVED</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>失敗の理由</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>保存した配置を読み込めませんでした。</t>
-        </is>
-      </c>
       <c r="D18" s="8" t="n"/>
       <c r="E18" s="9" t="inlineStr">
         <is>
@@ -1095,7 +1096,7 @@
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>REASON_WRITE</t>
+          <t>REASON_SAVE_CURRENT</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1105,7 +1106,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdocker用のレイアウトを書き出せませんでした。</t>
+          <t>現在の配置を本体に保存させることができませんでした。</t>
         </is>
       </c>
       <c r="D19" s="8" t="n"/>
@@ -1118,7 +1119,7 @@
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>REASON_LOAD_FAILED</t>
+          <t>REASON_REGISTER</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -1128,7 +1129,7 @@
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>本体がレイアウトの読み込みに失敗しました。</t>
+          <t>TP_GUIdocker用のレイアウトを本体に登録できませんでした。</t>
         </is>
       </c>
       <c r="D20" s="8" t="n"/>
@@ -1141,7 +1142,7 @@
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>REASON_NOT_IN_MENU</t>
+          <t>REASON_READ_SAVED</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
@@ -1151,7 +1152,7 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>TP_GUIdocker用のレイアウトがメニューに見つかりません。</t>
+          <t>保存した配置を読み込めませんでした。</t>
         </is>
       </c>
       <c r="D21" s="8" t="n"/>
@@ -1164,17 +1165,17 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>REASON_MISSING</t>
+          <t>REASON_WRITE</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>失敗の理由 (%s は切り離されなかったパネル)</t>
+          <t>失敗の理由</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>一部のパネルが本体に切り離されませんでした (%s)。</t>
+          <t>TP_GUIdocker用のレイアウトを書き出せませんでした。</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
@@ -1187,17 +1188,17 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>REASON_CAPTURE</t>
+          <t>REASON_LOAD_FAILED</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>失敗の理由 (%s はパネル)</t>
+          <t>失敗の理由</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>パネル(%s)を取り込めませんでした。</t>
+          <t>本体がレイアウトの読み込みに失敗しました。</t>
         </is>
       </c>
       <c r="D23" s="8" t="n"/>
@@ -1207,92 +1208,92 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="18" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
+          <t>REASON_NOT_IN_MENU</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>失敗の理由</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>TP_GUIdocker用のレイアウトがメニューに見つかりません。</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>REASON_MISSING</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>失敗の理由 (%s は切り離されなかったパネル)</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>一部のパネルが本体に切り離されませんでした (%s)。</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n"/>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>REASON_CAPTURE</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>失敗の理由 (%s はパネル)</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>パネル(%s)を取り込めませんでした。</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
           <t>EXPLORER_NOTICE</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>有効中にメディアエクスプローラーを開こうとした時の案内</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>メディアエクスプローラーは、TP_GUIdockerの有効中は使えません。
 「編集」→「プラグイン」→「TP_GUIdocker」→「TP_GUIdockerを無効化」で標準の画面に戻すと使えます。</t>
         </is>
       </c>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>TAB_FLOAT</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>タブの右クリックメニュー</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>分離する</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>TAB_CLOSE</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>タブの右クリックメニュー</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>閉じる</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>TAB_MOVE_TO</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>タブの右クリックメニュー (下に区画の一覧が出る)</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>他の区画へ移動</t>
-        </is>
-      </c>
       <c r="D27" s="8" t="n"/>
       <c r="E27" s="9" t="inlineStr">
         <is>
@@ -1303,17 +1304,17 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>TAB_SPLIT</t>
+          <t>TAB_FLOAT</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>タブの右クリックメニュー (下に分割の向きが出る)</t>
+          <t>タブの右クリックメニュー</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>この区画を分割</t>
+          <t>分離する</t>
         </is>
       </c>
       <c r="D28" s="8" t="n"/>
@@ -1326,17 +1327,17 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>SPLIT_LEFT</t>
+          <t>TAB_CLOSE</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>「この区画を分割」の下の項目</t>
+          <t>タブの右クリックメニュー</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>左に空き区画を作る</t>
+          <t>閉じる</t>
         </is>
       </c>
       <c r="D29" s="8" t="n"/>
@@ -1349,17 +1350,17 @@
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>SPLIT_RIGHT</t>
+          <t>TAB_MOVE_TO</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>「この区画を分割」の下の項目</t>
+          <t>タブの右クリックメニュー (下に区画の一覧が出る)</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>右に空き区画を作る</t>
+          <t>他の区画へ移動</t>
         </is>
       </c>
       <c r="D30" s="8" t="n"/>
@@ -1372,17 +1373,17 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>SPLIT_TOP</t>
+          <t>TAB_SPLIT</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>「この区画を分割」の下の項目</t>
+          <t>タブの右クリックメニュー (下に分割の向きが出る)</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>上に空き区画を作る</t>
+          <t>この区画を分割</t>
         </is>
       </c>
       <c r="D31" s="8" t="n"/>
@@ -1395,7 +1396,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>SPLIT_BOTTOM</t>
+          <t>SPLIT_LEFT</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -1405,7 +1406,7 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>下に空き区画を作る</t>
+          <t>左に空き区画を作る</t>
         </is>
       </c>
       <c r="D32" s="8" t="n"/>
@@ -1418,17 +1419,17 @@
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>AREA_NAME_FORMAT</t>
+          <t>SPLIT_RIGHT</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>「他の区画へ移動」の一覧での区画の呼び名 (%s は区画の表示中パネル名)</t>
+          <t>「この区画を分割」の下の項目</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>%sの区画</t>
+          <t>右に空き区画を作る</t>
         </is>
       </c>
       <c r="D33" s="8" t="n"/>
@@ -1441,17 +1442,17 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>AREA_NAME_EMPTY</t>
+          <t>SPLIT_TOP</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>同上 (空き区画の呼び名。%d は番号)</t>
+          <t>「この区画を分割」の下の項目</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>空き区画%d</t>
+          <t>上に空き区画を作る</t>
         </is>
       </c>
       <c r="D34" s="8" t="n"/>
@@ -1464,17 +1465,17 @@
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>AREA_CLOSE</t>
+          <t>SPLIT_BOTTOM</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>空き区画の右クリックメニュー</t>
+          <t>「この区画を分割」の下の項目</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>この区画を閉じる</t>
+          <t>下に空き区画を作る</t>
         </is>
       </c>
       <c r="D35" s="8" t="n"/>
@@ -1484,92 +1485,92 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="18" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
+          <t>AREA_NAME_FORMAT</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>「他の区画へ移動」の一覧での区画の呼び名 (%s は区画の表示中パネル名)</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>%sの区画</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>AREA_NAME_EMPTY</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>同上 (空き区画の呼び名。%d は番号)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>空き区画%d</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>AREA_CLOSE</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>空き区画の右クリックメニュー</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>この区画を閉じる</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
           <t>DOCK_UNKNOWN_PANEL</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>照合できなかった浮いた窓を区画へ入れようとした時の知らせ</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>このパネルは識別できないため、区画に入れられません。
 一度閉じて「表示」メニューから開き直してください。</t>
         </is>
       </c>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>WS_DEFAULT_NAME</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>最初のワークスペースの名前</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>標準</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>WS_NEW_NAME</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>「＋」で作るワークスペースの名前の初期値 (%d は番号)</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>ワークスペース%d</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>WS_ADD</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>ワークスペースの帯の追加ボタン</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr">
-        <is>
-          <t>＋</t>
-        </is>
-      </c>
       <c r="D39" s="8" t="n"/>
       <c r="E39" s="9" t="inlineStr">
         <is>
@@ -1580,17 +1581,17 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>WS_MENU_RENAME</t>
+          <t>WS_DEFAULT_NAME</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>ワークスペースのボタンの右クリックメニュー</t>
+          <t>最初のワークスペースの名前</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>名前を変更</t>
+          <t>標準</t>
         </is>
       </c>
       <c r="D40" s="8" t="n"/>
@@ -1603,17 +1604,17 @@
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>WS_MENU_SAVE</t>
+          <t>WS_NEW_NAME</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>「＋」で作るワークスペースの名前の初期値 (%d は番号)</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>今の配置で上書き保存</t>
+          <t>ワークスペース%d</t>
         </is>
       </c>
       <c r="D41" s="8" t="n"/>
@@ -1626,17 +1627,17 @@
     <row r="42" ht="18" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>WS_MENU_RESET</t>
+          <t>WS_ADD</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>ワークスペースの帯の追加ボタン</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>保存時の配置に戻す</t>
+          <t>＋</t>
         </is>
       </c>
       <c r="D42" s="8" t="n"/>
@@ -1649,17 +1650,17 @@
     <row r="43" ht="18" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>WS_MENU_DELETE</t>
+          <t>WS_MENU_RENAME</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>ワークスペースのボタンの右クリックメニュー</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>削除</t>
+          <t>名前を変更</t>
         </is>
       </c>
       <c r="D43" s="8" t="n"/>
@@ -1672,17 +1673,17 @@
     <row r="44" ht="18" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>WS_DELETE_CONFIRM</t>
+          <t>WS_MENU_SAVE</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>ワークスペースを削除する時の確認 (%s は名前)</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>ワークスペース「%s」を削除しますか？</t>
+          <t>今の配置で上書き保存</t>
         </is>
       </c>
       <c r="D44" s="8" t="n"/>
@@ -1695,17 +1696,17 @@
     <row r="45" ht="18" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>WS_DELETE_LAST</t>
+          <t>WS_MENU_RESET</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>最後の1つを削除しようとした時の知らせ</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>最後のワークスペースは削除できません。</t>
+          <t>保存時の配置に戻す</t>
         </is>
       </c>
       <c r="D45" s="8" t="n"/>
@@ -1718,17 +1719,17 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>WS_NAME_TITLE</t>
+          <t>WS_MENU_DELETE</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>名前を入力する画面の題名</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>ワークスペースの名前</t>
+          <t>削除</t>
         </is>
       </c>
       <c r="D46" s="8" t="n"/>
@@ -1741,17 +1742,17 @@
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>WS_NAME_LABEL</t>
+          <t>WS_DELETE_CONFIRM</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>名前を入力する画面の説明</t>
+          <t>ワークスペースを削除する時の確認 (%s は名前)</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>名前:</t>
+          <t>ワークスペース「%s」を削除しますか？</t>
         </is>
       </c>
       <c r="D47" s="8" t="n"/>
@@ -1764,17 +1765,17 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>BUTTON_OK</t>
+          <t>WS_DELETE_LAST</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>名前を入力する画面のボタン</t>
+          <t>最後の1つを削除しようとした時の知らせ</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>最後のワークスペースは削除できません。</t>
         </is>
       </c>
       <c r="D48" s="8" t="n"/>
@@ -1787,17 +1788,17 @@
     <row r="49" ht="18" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>BUTTON_CANCEL</t>
+          <t>WS_NAME_TITLE</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>名前を入力する画面のボタン</t>
+          <t>名前を入力する画面の題名</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>キャンセル</t>
+          <t>ワークスペースの名前</t>
         </is>
       </c>
       <c r="D49" s="8" t="n"/>
@@ -1807,20 +1808,20 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
+    <row r="50" ht="18" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>MENU_WS_SWITCH</t>
+          <t>WS_NAME_LABEL</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」→「ワークスペース」の項目 (ショートカットキー割り当て用。%d は番号)</t>
+          <t>名前を入力する画面の説明</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>ワークスペース%dに切り替え</t>
+          <t>名前:</t>
         </is>
       </c>
       <c r="D50" s="8" t="n"/>
@@ -1830,20 +1831,20 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="18" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>MENU_WS_GROUP</t>
+          <t>BUTTON_OK</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニュー内の小分けの見出し (ワークスペース1〜9に切り替え)</t>
+          <t>名前を入力する画面のボタン</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>ワークスペース</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D51" s="8" t="n"/>
@@ -1853,20 +1854,20 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
+    <row r="52" ht="18" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>MENU_MAXIMIZE</t>
+          <t>BUTTON_CANCEL</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニューの項目 (ショートカットキー割り当て用。カーソルの下のパネルを最大化・元に戻す)</t>
+          <t>名前を入力する画面のボタン</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>パネルを最大化・元に戻す</t>
+          <t>キャンセル</t>
         </is>
       </c>
       <c r="D52" s="8" t="n"/>
@@ -1876,20 +1877,20 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="18" customHeight="1">
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>TAB_MAXIMIZE</t>
+          <t>MENU_WS_SWITCH</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>タブの右クリックメニュー (通常時)</t>
+          <t>「TP_GUIdocker」→「ワークスペース」の項目 (ショートカットキー割り当て用。%d は番号)</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>最大化</t>
+          <t>ワークスペース%dに切り替え</t>
         </is>
       </c>
       <c r="D53" s="8" t="n"/>
@@ -1899,20 +1900,20 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="18" customHeight="1">
+    <row r="54" ht="30" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>TAB_RESTORE</t>
+          <t>MENU_WS_GROUP</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>タブの右クリックメニュー (最大化中)</t>
+          <t>「TP_GUIdocker」メニュー内の小分けの見出し (ワークスペース1〜9に切り替え)</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>元の大きさに戻す</t>
+          <t>ワークスペース</t>
         </is>
       </c>
       <c r="D54" s="8" t="n"/>
@@ -1922,20 +1923,20 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="18" customHeight="1">
+    <row r="55" ht="30" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>MENU_LOCK</t>
+          <t>MENU_MAXIMIZE</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニューの切り替え項目 (ロックしていない時)</t>
+          <t>「TP_GUIdocker」メニューの項目 (ショートカットキー割り当て用。カーソルの下のパネルを最大化・元に戻す)</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>レイアウトをロック</t>
+          <t>パネルを最大化・元に戻す</t>
         </is>
       </c>
       <c r="D55" s="8" t="n"/>
@@ -1948,17 +1949,17 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>MENU_UNLOCK</t>
+          <t>TAB_MAXIMIZE</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>同上 (ロック中)</t>
+          <t>タブの右クリックメニュー (通常時)</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>レイアウトのロックを解除</t>
+          <t>最大化</t>
         </is>
       </c>
       <c r="D56" s="8" t="n"/>
@@ -1968,20 +1969,20 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="30" customHeight="1">
+    <row r="57" ht="18" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>LOCK_BADGE</t>
+          <t>TAB_RESTORE</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>ロック中、帯の右端の閉じた錠前の絵にカーソルを乗せると出る説明 (クリックで解除)</t>
+          <t>タブの右クリックメニュー (最大化中)</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>ロック中 (クリックで解除)</t>
+          <t>元の大きさに戻す</t>
         </is>
       </c>
       <c r="D57" s="8" t="n"/>
@@ -1991,20 +1992,20 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
+    <row r="58" ht="18" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>UNLOCK_BADGE</t>
+          <t>MENU_LOCK</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>ロックしていない時、帯の右端の開いた錠前の絵にカーソルを乗せると出る説明 (クリックでロック)</t>
+          <t>「TP_GUIdocker」メニューの切り替え項目 (ロックしていない時)</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>クリックでレイアウトをロック</t>
+          <t>レイアウトをロック</t>
         </is>
       </c>
       <c r="D58" s="8" t="n"/>
@@ -2017,17 +2018,17 @@
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>MENU_EXPORT_SAMPLES</t>
+          <t>MENU_UNLOCK</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニューの項目 (見本の画像を書き出す。指示用)</t>
+          <t>同上 (ロック中)</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>見本を書き出す</t>
+          <t>レイアウトのロックを解除</t>
         </is>
       </c>
       <c r="D59" s="8" t="n"/>
@@ -2037,92 +2038,92 @@
         </is>
       </c>
     </row>
-    <row r="60" ht="45" customHeight="1">
+    <row r="60" ht="30" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
+          <t>LOCK_BADGE</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>ロック中、帯の右端の閉じた錠前の絵にカーソルを乗せると出る説明 (クリックで解除)</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>ロック中 (クリックで解除)</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="n"/>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>UNLOCK_BADGE</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>ロックしていない時、帯の右端の開いた錠前の絵にカーソルを乗せると出る説明 (クリックでロック)</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>クリックでレイアウトをロック</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>MENU_EXPORT_SAMPLES</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニューの項目 (見本の画像を書き出す。指示用)</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>見本を書き出す</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
           <t>EXPORT_DONE</t>
         </is>
       </c>
-      <c r="B60" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>見本を書き出した時の知らせ (%s は書き出し先)</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>見本を書き出しました。
 書き出し先: %s</t>
         </is>
       </c>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>EXPORT_NEED_ACTIVE</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>無効中に見本を書き出そうとした時の知らせ</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>見本は TP_GUIdockerの有効中に書き出せます。</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>WS_MENU_COLOR</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>ワークスペースのボタンの右クリックメニュー・「TP_GUIdocker」メニュー</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>テーマの色を変える…</t>
-        </is>
-      </c>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>実装済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>WS_MENU_COLOR_RESET</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>テーマの色を本体設定に戻す</t>
-        </is>
-      </c>
       <c r="D63" s="8" t="n"/>
       <c r="E63" s="9" t="inlineStr">
         <is>
@@ -2130,20 +2131,20 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="30" customHeight="1">
+    <row r="64" ht="18" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>MENU_GROUP_VIEW</t>
+          <t>EXPORT_NEED_ACTIVE</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニュー内の小分けの見出し (ドラッグ時の表示・テーマの色)</t>
+          <t>無効中に見本を書き出そうとした時の知らせ</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>表示の設定</t>
+          <t>見本は TP_GUIdockerの有効中に書き出せます。</t>
         </is>
       </c>
       <c r="D64" s="8" t="n"/>
@@ -2156,17 +2157,17 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>MENU_GROUP_LAYOUT</t>
+          <t>WS_MENU_COLOR</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニュー内の小分けの見出し (配置を初期状態に戻す・無効時のレイアウトを選ぶ)</t>
+          <t>ワークスペースのボタンの右クリックメニュー・「TP_GUIdocker」メニュー</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>配置の設定</t>
+          <t>テーマの色を変える…</t>
         </is>
       </c>
       <c r="D65" s="8" t="n"/>
@@ -2179,17 +2180,17 @@
     <row r="66" ht="18" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>MENU_GROUP_TOOLS</t>
+          <t>WS_MENU_COLOR_RESET</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>「TP_GUIdocker」メニュー内の小分けの見出し (見本を書き出す)</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>指示用</t>
+          <t>テーマの色を本体設定に戻す</t>
         </is>
       </c>
       <c r="D66" s="8" t="n"/>
@@ -2199,8 +2200,77 @@
         </is>
       </c>
     </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>MENU_GROUP_VIEW</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニュー内の小分けの見出し (ドラッグ時の表示・テーマの色)</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>表示の設定</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>MENU_GROUP_LAYOUT</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニュー内の小分けの見出し (配置を初期状態に戻す・無効時のレイアウトを選ぶ)</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>配置の設定</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>MENU_GROUP_TOOLS</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>「TP_GUIdocker」メニュー内の小分けの見出し (見本を書き出す)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>指示用</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n"/>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>実装済み</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E66"/>
+  <autoFilter ref="A1:E69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
